--- a/output/pdf_financials_xlsx/EGT.xlsx
+++ b/output/pdf_financials_xlsx/EGT.xlsx
@@ -4597,31 +4597,31 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.108966</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.096099</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.128834</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.124173</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.122309</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.126049</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.152888</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.244358</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-0.143392</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>-0.224127</v>
@@ -13052,7 +13052,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -15960,7 +15964,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -18142,7 +18150,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EGT.xlsx
+++ b/output/pdf_financials_xlsx/EGT.xlsx
@@ -2100,31 +2100,31 @@
         <v>0.561373</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.399874</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.05596</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.502459</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.355471</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.568346</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.48017</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.603922</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>15.035483</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.814003</v>
@@ -2186,31 +2186,31 @@
         <v>0.561373</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.399874</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.05596</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.502459</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>4.355471</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.568346</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.286</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.48017</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.603922</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>15.035483</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.814003</v>
@@ -2702,28 +2702,28 @@
         <v>1.579837</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.141876</v>
+        <v>0.7420020000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.171114</v>
+        <v>2.115154</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.72535</v>
+        <v>1.222891</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.573723</v>
+        <v>0.218252</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.842905</v>
+        <v>0.274559</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.800469</v>
+        <v>0.514469</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.9711920000000001</v>
+        <v>0.491022</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>36.388379</v>
+        <v>31.784457</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">

--- a/output/pdf_financials_xlsx/EGT.xlsx
+++ b/output/pdf_financials_xlsx/EGT.xlsx
@@ -1597,15 +1597,11 @@
       <c r="K23" s="3" t="n">
         <v>-16.828272</v>
       </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L23" s="3" t="n">
+        <v>-32.41878</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>-15.381361</v>
       </c>
     </row>
     <row r="24">
@@ -4935,15 +4931,11 @@
       <c r="K99" s="3" t="n">
         <v>-16.828272</v>
       </c>
-      <c r="L99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L99" s="3" t="n">
+        <v>-32.41878</v>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>-15.381361</v>
       </c>
     </row>
     <row r="100">
@@ -21834,7 +21826,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -24890,7 +24886,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
